--- a/Etapa Elaboración - Iteración 2/Casos de prueba - Kairos - NexTech.xlsx
+++ b/Etapa Elaboración - Iteración 2/Casos de prueba - Kairos - NexTech.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="CU01- Iniciar Sesión" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="CU20- Registrar tiempo por cron" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="43">
   <si>
     <t>Condición</t>
   </si>
@@ -137,13 +138,16 @@
   </si>
   <si>
     <t>El sistema denega el acceso al usuario y lo regresa a la pantalla de iniciar sesión. Muestra un mensaje de error.</t>
+  </si>
+  <si>
+    <t>Flujo básico</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -159,8 +163,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -171,6 +180,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
         <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE5CD"/>
+        <bgColor rgb="FFFCE5CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -194,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -210,6 +225,18 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -219,6 +246,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -662,4 +693,143 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.88"/>
+    <col customWidth="1" min="2" max="2" width="27.25"/>
+    <col customWidth="1" min="5" max="5" width="17.63"/>
+    <col customWidth="1" min="6" max="6" width="15.88"/>
+    <col customWidth="1" min="7" max="7" width="32.5"/>
+    <col customWidth="1" min="8" max="8" width="29.5"/>
+    <col customWidth="1" min="9" max="9" width="19.75"/>
+    <col customWidth="1" min="11" max="11" width="21.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" ht="78.75" customHeight="1">
+      <c r="A2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="8"/>
+    </row>
+    <row r="3" ht="76.5" customHeight="1">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="8"/>
+    </row>
+    <row r="4" ht="60.75" customHeight="1">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" ht="67.5" customHeight="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="8"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>